--- a/144F20/Topic 3/ConstantGrowthRate.xlsx
+++ b/144F20/Topic 3/ConstantGrowthRate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail-my.sharepoint.com/personal/richard_ketchersid_gcu_edu/Documents/Course Materials/git/Teaching/144F20/Topic 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:80_{FE07CE70-4AD8-4729-8CEC-9EA745513535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="10_ncr:80_{FE07CE70-4AD8-4729-8CEC-9EA745513535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85967B8F-FE5C-49AE-977A-84CE943D66EB}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="1365" windowWidth="24750" windowHeight="14070" xr2:uid="{0E835B87-0F00-4DF3-8488-BA3E1D614520}"/>
+    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{0E835B87-0F00-4DF3-8488-BA3E1D614520}"/>
   </bookViews>
   <sheets>
     <sheet name="Constant Change" sheetId="1" r:id="rId1"/>
@@ -1256,53 +1256,116 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1331,28 +1394,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1409,48 +1451,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2431,8 +2431,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3993173" y="3259015"/>
-              <a:ext cx="4572000" cy="2875085"/>
+              <a:off x="3987458" y="3262825"/>
+              <a:ext cx="4572000" cy="2871275"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2466,9 +2466,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2506,7 +2506,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2612,7 +2612,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2754,7 +2754,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2771,108 +2771,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21.75" thickBot="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="122" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="72" t="s">
+      <c r="E1" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="75"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="E2" s="109" t="s">
+      <c r="E2" s="76" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="110"/>
-      <c r="K2" s="111"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="E3" s="112"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="113"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="K3" s="114"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="81"/>
     </row>
     <row r="4" spans="1:16" ht="20.25" customHeight="1" thickBot="1">
-      <c r="E4" s="115"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
-      <c r="M4" s="59" t="s">
+      <c r="E4" s="82"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="84"/>
+      <c r="M4" s="91" t="s">
         <v>76</v>
       </c>
-      <c r="N4" s="59"/>
-      <c r="O4" s="59"/>
+      <c r="N4" s="91"/>
+      <c r="O4" s="91"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="E5" s="109" t="s">
+      <c r="E5" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="111"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="59"/>
-      <c r="O5" s="59"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="78"/>
+      <c r="M5" s="91"/>
+      <c r="N5" s="91"/>
+      <c r="O5" s="91"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16" ht="21.75" customHeight="1" thickBot="1">
-      <c r="E6" s="115"/>
-      <c r="F6" s="116"/>
-      <c r="G6" s="116"/>
-      <c r="H6" s="116"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="116"/>
-      <c r="K6" s="117"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="84"/>
     </row>
     <row r="7" spans="1:16" ht="15.75" thickBot="1">
       <c r="A7" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="68"/>
+      <c r="C7" s="65"/>
       <c r="D7" s="33" t="s">
         <v>1</v>
       </c>
       <c r="E7" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="66" t="s">
+      <c r="F7" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="67"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="66" t="s">
+      <c r="G7" s="72"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="67"/>
-      <c r="K7" s="67"/>
-      <c r="L7" s="68"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="72"/>
+      <c r="L7" s="65"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="5">
@@ -2890,10 +2890,10 @@
       <c r="F8" s="69"/>
       <c r="G8" s="70"/>
       <c r="H8" s="71"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="62"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="68"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="5">
@@ -2914,19 +2914,19 @@
         <f t="shared" ref="E9:E18" ca="1" si="1">C9/C8-1</f>
         <v>3.1712204007285916E-2</v>
       </c>
-      <c r="F9" s="60" t="str">
+      <c r="F9" s="66" t="str">
         <f ca="1">B9&amp;" = "&amp;B8&amp;" + "&amp;ROUND(D9,2)</f>
         <v>Q₁ = Q₀ + 34.82</v>
       </c>
-      <c r="G9" s="61"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="60" t="str">
+      <c r="G9" s="67"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="66" t="str">
         <f ca="1">B9&amp;" = "&amp;B8&amp;" + "&amp;B8&amp;"∙("&amp;ROUND(E9*100,2)&amp;"%) = "&amp;B8&amp;"∙(1 + "&amp;ROUND(E9*100,2)&amp;"%)"</f>
         <v>Q₁ = Q₀ + Q₀∙(3.17%) = Q₀∙(1 + 3.17%)</v>
       </c>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
-      <c r="L9" s="62"/>
+      <c r="J9" s="67"/>
+      <c r="K9" s="67"/>
+      <c r="L9" s="68"/>
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:16">
@@ -2948,19 +2948,19 @@
         <f t="shared" ca="1" si="1"/>
         <v>3.0737451669285543E-2</v>
       </c>
-      <c r="F10" s="60" t="str">
+      <c r="F10" s="66" t="str">
         <f ca="1">B10&amp;" = "&amp;B9&amp;" + "&amp;ROUND(D10,2)&amp;" = "&amp;B$8&amp;" + "&amp;A10&amp;"∙("&amp;ROUND(D10,2)&amp;")"</f>
         <v>Q₂ = Q₁ + 34.82 = Q₀ + 2∙(34.82)</v>
       </c>
-      <c r="G10" s="61"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="60" t="str">
+      <c r="G10" s="67"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="66" t="str">
         <f ca="1">B10&amp;" = "&amp;B9&amp;" + "&amp;B9&amp;"∙("&amp;ROUND(E10*100,2)&amp;"%) = "&amp;B9&amp;"∙(1 + "&amp;ROUND(E10*100,2)&amp;"%)"</f>
         <v>Q₂ = Q₁ + Q₁∙(3.07%) = Q₁∙(1 + 3.07%)</v>
       </c>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="62"/>
+      <c r="J10" s="67"/>
+      <c r="K10" s="67"/>
+      <c r="L10" s="68"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="1:16">
@@ -2982,19 +2982,19 @@
         <f t="shared" ca="1" si="1"/>
         <v>2.9820835188927974E-2</v>
       </c>
-      <c r="F11" s="60" t="str">
+      <c r="F11" s="66" t="str">
         <f ca="1">B11&amp;" = "&amp;B10&amp;" + "&amp;ROUND(D11,2)&amp;" = "&amp;B$8&amp;" + "&amp;A11&amp;"∙("&amp;ROUND(D11,2)&amp;")"</f>
         <v>Q₃ = Q₂ + 34.82 = Q₀ + 3∙(34.82)</v>
       </c>
-      <c r="G11" s="61"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="60" t="str">
+      <c r="G11" s="67"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="66" t="str">
         <f t="shared" ref="I11:I17" ca="1" si="2">B11&amp;" = "&amp;B10&amp;" + "&amp;B10&amp;"∙("&amp;ROUND(E11*100,2)&amp;"%) = "&amp;B10&amp;"∙(1 + "&amp;ROUND(E11*100,2)&amp;"%)"</f>
         <v>Q₃ = Q₂ + Q₂∙(2.98%) = Q₂∙(1 + 2.98%)</v>
       </c>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="62"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="68"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="1:16">
@@ -3016,19 +3016,19 @@
         <f t="shared" ca="1" si="1"/>
         <v>2.8957304193070854E-2</v>
       </c>
-      <c r="F12" s="60" t="str">
+      <c r="F12" s="66" t="str">
         <f t="shared" ref="F12:F18" ca="1" si="3">B12&amp;" = "&amp;B11&amp;" + "&amp;ROUND(D12,2)&amp;" = "&amp;B$8&amp;" + "&amp;A12&amp;"∙("&amp;ROUND(D12,2)&amp;")"</f>
         <v>Q₄ = Q₃ + 34.82 = Q₀ + 4∙(34.82)</v>
       </c>
-      <c r="G12" s="61"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="60" t="str">
+      <c r="G12" s="67"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="66" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Q₄ = Q₃ + Q₃∙(2.9%) = Q₃∙(1 + 2.9%)</v>
       </c>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
-      <c r="L12" s="62"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
+      <c r="L12" s="68"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="1:16">
@@ -3050,19 +3050,19 @@
         <f t="shared" ca="1" si="1"/>
         <v>2.8142376826587379E-2</v>
       </c>
-      <c r="F13" s="60" t="str">
+      <c r="F13" s="66" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>Q₅ = Q₄ + 34.82 = Q₀ + 5∙(34.82)</v>
       </c>
-      <c r="G13" s="61"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="60" t="str">
+      <c r="G13" s="67"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="66" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Q₅ = Q₄ + Q₄∙(2.81%) = Q₄∙(1 + 2.81%)</v>
       </c>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="62"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="67"/>
+      <c r="L13" s="68"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="1:16" ht="15.6" customHeight="1">
@@ -3084,19 +3084,19 @@
         <f t="shared" ca="1" si="1"/>
         <v>2.7372061944815673E-2</v>
       </c>
-      <c r="F14" s="60" t="str">
+      <c r="F14" s="66" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>Q₆ = Q₅ + 34.82 = Q₀ + 6∙(34.82)</v>
       </c>
-      <c r="G14" s="61"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="60" t="str">
+      <c r="G14" s="67"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="66" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Q₆ = Q₅ + Q₅∙(2.74%) = Q₅∙(1 + 2.74%)</v>
       </c>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="62"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="67"/>
+      <c r="L14" s="68"/>
       <c r="M14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="15.6" customHeight="1">
@@ -3118,19 +3118,19 @@
         <f t="shared" ca="1" si="1"/>
         <v>2.6642793744070081E-2</v>
       </c>
-      <c r="F15" s="60" t="str">
+      <c r="F15" s="66" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>Q₇ = Q₆ + 34.82 = Q₀ + 7∙(34.82)</v>
       </c>
-      <c r="G15" s="61"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="60" t="str">
+      <c r="G15" s="67"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="66" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Q₇ = Q₆ + Q₆∙(2.66%) = Q₆∙(1 + 2.66%)</v>
       </c>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="62"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="68"/>
       <c r="M15" s="1"/>
     </row>
     <row r="16" spans="1:16" ht="15.6" customHeight="1">
@@ -3152,19 +3152,19 @@
         <f t="shared" ca="1" si="1"/>
         <v>2.5951376570721552E-2</v>
       </c>
-      <c r="F16" s="60" t="str">
+      <c r="F16" s="66" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>Q₈ = Q₇ + 34.82 = Q₀ + 8∙(34.82)</v>
       </c>
-      <c r="G16" s="61"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="60" t="str">
+      <c r="G16" s="67"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="66" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Q₈ = Q₇ + Q₇∙(2.6%) = Q₇∙(1 + 2.6%)</v>
       </c>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="62"/>
+      <c r="J16" s="67"/>
+      <c r="K16" s="67"/>
+      <c r="L16" s="68"/>
       <c r="M16" s="1"/>
     </row>
     <row r="17" spans="1:13" ht="15.6" customHeight="1">
@@ -3186,19 +3186,19 @@
         <f t="shared" ca="1" si="1"/>
         <v>2.5294938106584564E-2</v>
       </c>
-      <c r="F17" s="60" t="str">
+      <c r="F17" s="66" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>Q₉ = Q₈ + 34.82 = Q₀ + 9∙(34.82)</v>
       </c>
-      <c r="G17" s="61"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="60" t="str">
+      <c r="G17" s="67"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="66" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Q₉ = Q₈ + Q₈∙(2.53%) = Q₈∙(1 + 2.53%)</v>
       </c>
-      <c r="J17" s="61"/>
-      <c r="K17" s="61"/>
-      <c r="L17" s="62"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="67"/>
+      <c r="L17" s="68"/>
       <c r="M17" s="1"/>
     </row>
     <row r="18" spans="1:13" ht="15.6" customHeight="1">
@@ -3220,19 +3220,19 @@
         <f t="shared" ca="1" si="1"/>
         <v>2.4670889484051051E-2</v>
       </c>
-      <c r="F18" s="60" t="str">
+      <c r="F18" s="66" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>Q₁₀ = Q₉ + 34.82 = Q₀ + 10∙(34.82)</v>
       </c>
-      <c r="G18" s="61"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="60" t="str">
+      <c r="G18" s="67"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="66" t="str">
         <f ca="1">B18&amp;" = "&amp;B17&amp;" + "&amp;B17&amp;"∙("&amp;ROUND(E18*100,2)&amp;"%) = "&amp;B17&amp;"∙(1 + "&amp;ROUND(E18*100,2)&amp;"%)"</f>
         <v>Q₁₀ = Q₉ + Q₉∙(2.47%) = Q₉∙(1 + 2.47%)</v>
       </c>
-      <c r="J18" s="61"/>
-      <c r="K18" s="61"/>
-      <c r="L18" s="62"/>
+      <c r="J18" s="67"/>
+      <c r="K18" s="67"/>
+      <c r="L18" s="68"/>
       <c r="M18" s="1"/>
     </row>
     <row r="19" spans="1:13">
@@ -3251,18 +3251,18 @@
       <c r="E19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="60" t="str">
+      <c r="F19" s="66" t="str">
         <f>A19</f>
         <v>⋮</v>
       </c>
-      <c r="G19" s="61"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="60" t="s">
+      <c r="G19" s="67"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="J19" s="61"/>
-      <c r="K19" s="61"/>
-      <c r="L19" s="62"/>
+      <c r="J19" s="67"/>
+      <c r="K19" s="67"/>
+      <c r="L19" s="68"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" thickBot="1">
       <c r="A20" s="7" t="s">
@@ -3272,25 +3272,25 @@
         <v>40</v>
       </c>
       <c r="C20" s="13"/>
-      <c r="D20" s="118">
+      <c r="D20" s="59">
         <f ca="1">D18</f>
         <v>34.819999999999936</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="87" t="str">
+      <c r="F20" s="85" t="str">
         <f ca="1">B20&amp;" = "&amp;B$8&amp;" + "&amp;A20&amp;"∙("&amp;ROUND(D20,2)&amp;")"</f>
         <v>Qₙ = Q₀ + n∙(34.82)</v>
       </c>
-      <c r="G20" s="88"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="63" t="s">
+      <c r="G20" s="86"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="65"/>
+      <c r="J20" s="89"/>
+      <c r="K20" s="89"/>
+      <c r="L20" s="90"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0"/>
@@ -3302,16 +3302,14 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="34">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="E2:K4"/>
-    <mergeCell ref="E5:K6"/>
+    <mergeCell ref="M4:O5"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I15:L15"/>
     <mergeCell ref="F20:H20"/>
     <mergeCell ref="F19:H19"/>
     <mergeCell ref="I7:L7"/>
@@ -3328,14 +3326,16 @@
     <mergeCell ref="I19:L19"/>
     <mergeCell ref="I20:L20"/>
     <mergeCell ref="I8:L8"/>
-    <mergeCell ref="M4:O5"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="E2:K4"/>
+    <mergeCell ref="E5:K6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="M4:O5" r:id="rId2" display="https://youtu.be/HoCMAoenzDw" xr:uid="{B7474ABE-EF49-4165-8D07-B721CC234856}"/>
@@ -3358,105 +3358,105 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" thickBot="1">
-      <c r="E1" s="72" t="s">
+      <c r="E1" s="73" t="s">
         <v>77</v>
       </c>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="68"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="65"/>
     </row>
     <row r="2" spans="1:17">
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="96" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="77"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="98"/>
     </row>
     <row r="3" spans="1:17" ht="15" customHeight="1">
-      <c r="E3" s="78"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="80"/>
-      <c r="M3" s="59" t="s">
+      <c r="E3" s="99"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="101"/>
+      <c r="M3" s="91" t="s">
         <v>76</v>
       </c>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
+      <c r="N3" s="91"/>
+      <c r="O3" s="91"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:17" ht="15.75" thickBot="1">
-      <c r="E4" s="81"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="83"/>
-      <c r="M4" s="59"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="59"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="104"/>
+      <c r="M4" s="91"/>
+      <c r="N4" s="91"/>
+      <c r="O4" s="91"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="E5" s="75" t="s">
+      <c r="E5" s="96" t="s">
         <v>85</v>
       </c>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
-      <c r="K5" s="77"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="97"/>
+      <c r="K5" s="98"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" thickBot="1">
-      <c r="E6" s="81"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="83"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="103"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="103"/>
+      <c r="K6" s="104"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" thickBot="1">
       <c r="A7" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="68"/>
+      <c r="C7" s="65"/>
       <c r="D7" s="33" t="s">
         <v>1</v>
       </c>
       <c r="E7" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="66" t="s">
+      <c r="F7" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="66" t="s">
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="67"/>
-      <c r="K7" s="67"/>
-      <c r="L7" s="67"/>
-      <c r="M7" s="68"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="72"/>
+      <c r="L7" s="72"/>
+      <c r="M7" s="65"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="5">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="61"/>
-      <c r="M8" s="62"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="67"/>
+      <c r="M8" s="68"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="5">
@@ -3499,20 +3499,20 @@
         <f t="shared" ref="E9:E18" ca="1" si="1">C9/C8-1</f>
         <v>3.4799999999999276E-3</v>
       </c>
-      <c r="F9" s="84" t="str">
+      <c r="F9" s="92" t="str">
         <f ca="1">B9&amp;" = "&amp;B8&amp;" + "&amp;ROUND(D9,2)</f>
         <v>Q₁ = Q₀ + 3.82</v>
       </c>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="60" t="str">
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="66" t="str">
         <f ca="1">B9&amp;" = "&amp;B8&amp;" + "&amp;B8&amp;"∙("&amp;ROUND(E9*100,2)&amp;"%) = "&amp;B8&amp;"∙(1 + "&amp;ROUND(E9*100,2)&amp;"%)"</f>
         <v>Q₁ = Q₀ + Q₀∙(0.35%) = Q₀∙(1 + 0.35%)</v>
       </c>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
-      <c r="L9" s="61"/>
-      <c r="M9" s="62"/>
+      <c r="J9" s="67"/>
+      <c r="K9" s="67"/>
+      <c r="L9" s="67"/>
+      <c r="M9" s="68"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="5">
@@ -3533,20 +3533,20 @@
         <f t="shared" ca="1" si="1"/>
         <v>3.4799999999999276E-3</v>
       </c>
-      <c r="F10" s="84" t="str">
+      <c r="F10" s="92" t="str">
         <f ca="1">B10&amp;" = "&amp;B9&amp;" + "&amp;ROUND(D10,2)&amp;""</f>
         <v>Q₂ = Q₁ + 3.83</v>
       </c>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
-      <c r="I10" s="60" t="str">
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="66" t="str">
         <f ca="1">B10&amp;" = "&amp;B9&amp;" + "&amp;B9&amp;"∙("&amp;ROUND(E10*100,2)&amp;"%) = "&amp;B9&amp;"∙(1 + "&amp;ROUND(E10*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E10*100,2)&amp;"%)²"</f>
         <v>Q₂ = Q₁ + Q₁∙(0.35%) = Q₁∙(1 + 0.35%) = Q₀∙(1 + 0.35%)²</v>
       </c>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="62"/>
+      <c r="J10" s="67"/>
+      <c r="K10" s="67"/>
+      <c r="L10" s="67"/>
+      <c r="M10" s="68"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="5">
@@ -3567,20 +3567,20 @@
         <f t="shared" ca="1" si="1"/>
         <v>3.4799999999999276E-3</v>
       </c>
-      <c r="F11" s="84" t="str">
+      <c r="F11" s="92" t="str">
         <f t="shared" ref="F11:F18" ca="1" si="2">B11&amp;" = "&amp;B10&amp;" + "&amp;ROUND(D11,2)&amp;""</f>
         <v>Q₃ = Q₂ + 3.85</v>
       </c>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="60" t="str">
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="66" t="str">
         <f ca="1">B11&amp;" = "&amp;B10&amp;" + "&amp;B10&amp;"∙("&amp;ROUND(E11*100,2)&amp;"%) = "&amp;B10&amp;"∙(1 + "&amp;ROUND(E11*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E11*100,2)&amp;"%)³"</f>
         <v>Q₃ = Q₂ + Q₂∙(0.35%) = Q₂∙(1 + 0.35%) = Q₀∙(1 + 0.35%)³</v>
       </c>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="61"/>
-      <c r="M11" s="62"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="67"/>
+      <c r="M11" s="68"/>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="5">
@@ -3601,20 +3601,20 @@
         <f t="shared" ca="1" si="1"/>
         <v>3.4799999999999276E-3</v>
       </c>
-      <c r="F12" s="84" t="str">
+      <c r="F12" s="92" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Q₄ = Q₃ + 3.86</v>
       </c>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="60" t="str">
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="66" t="str">
         <f ca="1">B12&amp;" = "&amp;B11&amp;" + "&amp;B11&amp;"∙("&amp;ROUND(E12*100,2)&amp;"%) = "&amp;B11&amp;"∙(1 + "&amp;ROUND(E12*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E12*100,2)&amp;"%)⁴"</f>
         <v>Q₄ = Q₃ + Q₃∙(0.35%) = Q₃∙(1 + 0.35%) = Q₀∙(1 + 0.35%)⁴</v>
       </c>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
-      <c r="L12" s="61"/>
-      <c r="M12" s="62"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
+      <c r="L12" s="67"/>
+      <c r="M12" s="68"/>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="5">
@@ -3635,20 +3635,20 @@
         <f t="shared" ca="1" si="1"/>
         <v>3.4799999999999276E-3</v>
       </c>
-      <c r="F13" s="84" t="str">
+      <c r="F13" s="92" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Q₅ = Q₄ + 3.87</v>
       </c>
-      <c r="G13" s="85"/>
-      <c r="H13" s="85"/>
-      <c r="I13" s="60" t="str">
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="66" t="str">
         <f ca="1">B13&amp;" = "&amp;B12&amp;" + "&amp;B12&amp;"∙("&amp;ROUND(E13*100,2)&amp;"%) = "&amp;B12&amp;"∙(1 + "&amp;ROUND(E13*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E13*100,2)&amp;"%)⁵"</f>
         <v>Q₅ = Q₄ + Q₄∙(0.35%) = Q₄∙(1 + 0.35%) = Q₀∙(1 + 0.35%)⁵</v>
       </c>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="61"/>
-      <c r="M13" s="62"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="67"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="68"/>
     </row>
     <row r="14" spans="1:17" ht="15.6" customHeight="1">
       <c r="A14" s="5">
@@ -3669,20 +3669,20 @@
         <f t="shared" ca="1" si="1"/>
         <v>3.4799999999999276E-3</v>
       </c>
-      <c r="F14" s="84" t="str">
+      <c r="F14" s="92" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Q₆ = Q₅ + 3.89</v>
       </c>
-      <c r="G14" s="85"/>
-      <c r="H14" s="85"/>
-      <c r="I14" s="60" t="str">
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="66" t="str">
         <f ca="1">B14&amp;" = "&amp;B13&amp;" + "&amp;B13&amp;"∙("&amp;ROUND(E14*100,2)&amp;"%) = "&amp;B13&amp;"∙(1 + "&amp;ROUND(E14*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E14*100,2)&amp;"%)⁶"</f>
         <v>Q₆ = Q₅ + Q₅∙(0.35%) = Q₅∙(1 + 0.35%) = Q₀∙(1 + 0.35%)⁶</v>
       </c>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="61"/>
-      <c r="M14" s="62"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="67"/>
+      <c r="L14" s="67"/>
+      <c r="M14" s="68"/>
     </row>
     <row r="15" spans="1:17" ht="15.6" customHeight="1">
       <c r="A15" s="5">
@@ -3703,20 +3703,20 @@
         <f t="shared" ca="1" si="1"/>
         <v>3.4799999999999276E-3</v>
       </c>
-      <c r="F15" s="84" t="str">
+      <c r="F15" s="92" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Q₇ = Q₆ + 3.9</v>
       </c>
-      <c r="G15" s="85"/>
-      <c r="H15" s="85"/>
-      <c r="I15" s="60" t="str">
+      <c r="G15" s="93"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="66" t="str">
         <f ca="1">B15&amp;" = "&amp;B14&amp;" + "&amp;B14&amp;"∙("&amp;ROUND(E15*100,2)&amp;"%) = "&amp;B14&amp;"∙(1 + "&amp;ROUND(E15*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E15*100,2)&amp;"%)⁷"</f>
         <v>Q₇ = Q₆ + Q₆∙(0.35%) = Q₆∙(1 + 0.35%) = Q₀∙(1 + 0.35%)⁷</v>
       </c>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="61"/>
-      <c r="M15" s="62"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="67"/>
+      <c r="M15" s="68"/>
     </row>
     <row r="16" spans="1:17" ht="15.6" customHeight="1">
       <c r="A16" s="5">
@@ -3737,20 +3737,20 @@
         <f t="shared" ca="1" si="1"/>
         <v>3.4799999999999276E-3</v>
       </c>
-      <c r="F16" s="84" t="str">
+      <c r="F16" s="92" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Q₈ = Q₇ + 3.92</v>
       </c>
-      <c r="G16" s="85"/>
-      <c r="H16" s="85"/>
-      <c r="I16" s="60" t="str">
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="66" t="str">
         <f ca="1">B16&amp;" = "&amp;B15&amp;" + "&amp;B15&amp;"∙("&amp;ROUND(E16*100,2)&amp;"%) = "&amp;B15&amp;"∙(1 + "&amp;ROUND(E16*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E16*100,2)&amp;"%)⁸"</f>
         <v>Q₈ = Q₇ + Q₇∙(0.35%) = Q₇∙(1 + 0.35%) = Q₀∙(1 + 0.35%)⁸</v>
       </c>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="61"/>
-      <c r="M16" s="62"/>
+      <c r="J16" s="67"/>
+      <c r="K16" s="67"/>
+      <c r="L16" s="67"/>
+      <c r="M16" s="68"/>
     </row>
     <row r="17" spans="1:13" ht="15.6" customHeight="1">
       <c r="A17" s="5">
@@ -3771,20 +3771,20 @@
         <f t="shared" ca="1" si="1"/>
         <v>3.4799999999999276E-3</v>
       </c>
-      <c r="F17" s="84" t="str">
+      <c r="F17" s="92" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Q₉ = Q₈ + 3.93</v>
       </c>
-      <c r="G17" s="85"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="60" t="str">
+      <c r="G17" s="93"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="66" t="str">
         <f ca="1">B17&amp;" = "&amp;B16&amp;" + "&amp;B16&amp;"∙("&amp;ROUND(E17*100,2)&amp;"%) = "&amp;B16&amp;"∙(1 + "&amp;ROUND(E17*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E17*100,2)&amp;"%)⁹"</f>
         <v>Q₉ = Q₈ + Q₈∙(0.35%) = Q₈∙(1 + 0.35%) = Q₀∙(1 + 0.35%)⁹</v>
       </c>
-      <c r="J17" s="61"/>
-      <c r="K17" s="61"/>
-      <c r="L17" s="61"/>
-      <c r="M17" s="62"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="67"/>
+      <c r="L17" s="67"/>
+      <c r="M17" s="68"/>
     </row>
     <row r="18" spans="1:13" ht="15.6" customHeight="1">
       <c r="A18" s="5">
@@ -3805,20 +3805,20 @@
         <f t="shared" ca="1" si="1"/>
         <v>3.4799999999999276E-3</v>
       </c>
-      <c r="F18" s="84" t="str">
+      <c r="F18" s="92" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Q₁₀ = Q₉ + 3.94</v>
       </c>
-      <c r="G18" s="85"/>
-      <c r="H18" s="85"/>
-      <c r="I18" s="60" t="str">
+      <c r="G18" s="93"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="66" t="str">
         <f ca="1">B18&amp;" = "&amp;B17&amp;" + "&amp;B17&amp;"∙("&amp;ROUND(E18*100,2)&amp;"%) = "&amp;B17&amp;"∙(1 + "&amp;ROUND(E18*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E18*100,2)&amp;"%)¹⁰"</f>
         <v>Q₁₀ = Q₉ + Q₉∙(0.35%) = Q₉∙(1 + 0.35%) = Q₀∙(1 + 0.35%)¹⁰</v>
       </c>
-      <c r="J18" s="61"/>
-      <c r="K18" s="61"/>
-      <c r="L18" s="61"/>
-      <c r="M18" s="62"/>
+      <c r="J18" s="67"/>
+      <c r="K18" s="67"/>
+      <c r="L18" s="67"/>
+      <c r="M18" s="68"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="5" t="s">
@@ -3836,18 +3836,18 @@
       <c r="E19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="84" t="s">
+      <c r="F19" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="G19" s="85"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="60" t="s">
+      <c r="G19" s="93"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="J19" s="61"/>
-      <c r="K19" s="61"/>
-      <c r="L19" s="61"/>
-      <c r="M19" s="62"/>
+      <c r="J19" s="67"/>
+      <c r="K19" s="67"/>
+      <c r="L19" s="67"/>
+      <c r="M19" s="68"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" thickBot="1">
       <c r="A20" s="7" t="s">
@@ -3860,24 +3860,24 @@
       <c r="D20" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="119">
+      <c r="E20" s="60">
         <f ca="1">E18</f>
         <v>3.4799999999999276E-3</v>
       </c>
-      <c r="F20" s="90" t="str">
+      <c r="F20" s="94" t="str">
         <f>B20&amp;" = "&amp;B18&amp;" + "&amp;D20</f>
         <v>Qₙ = Q₁₀ + ???</v>
       </c>
-      <c r="G20" s="91"/>
-      <c r="H20" s="91"/>
-      <c r="I20" s="87" t="str">
+      <c r="G20" s="95"/>
+      <c r="H20" s="95"/>
+      <c r="I20" s="85" t="str">
         <f ca="1">B20&amp;" =  "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E20*100,2)&amp;"%)ⁿ"</f>
         <v>Qₙ =  Q₀∙(1 + 0.35%)ⁿ</v>
       </c>
-      <c r="J20" s="88"/>
-      <c r="K20" s="88"/>
-      <c r="L20" s="88"/>
-      <c r="M20" s="89"/>
+      <c r="J20" s="86"/>
+      <c r="K20" s="86"/>
+      <c r="L20" s="86"/>
+      <c r="M20" s="87"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0"/>
@@ -3889,6 +3889,23 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="33">
+    <mergeCell ref="M3:O4"/>
+    <mergeCell ref="I20:M20"/>
+    <mergeCell ref="I11:M11"/>
+    <mergeCell ref="I18:M18"/>
+    <mergeCell ref="I19:M19"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="E2:K4"/>
+    <mergeCell ref="E5:K6"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="F9:H9"/>
@@ -3905,23 +3922,6 @@
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="I10:M10"/>
     <mergeCell ref="F12:H12"/>
-    <mergeCell ref="I20:M20"/>
-    <mergeCell ref="I11:M11"/>
-    <mergeCell ref="I18:M18"/>
-    <mergeCell ref="I19:M19"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="E2:K4"/>
-    <mergeCell ref="E5:K6"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:M8"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="M3:O4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="M3:O4" r:id="rId2" display="https://youtu.be/HoCMAoenzDw" xr:uid="{D9262481-9EDA-481F-B42B-0C6411D8AE1E}"/>
@@ -3941,48 +3941,48 @@
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="21.140625" customWidth="1"/>
-    <col min="12" max="12" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1"/>
     <row r="2" spans="1:12" ht="18.75" thickBot="1">
-      <c r="F2" s="92" t="s">
+      <c r="F2" s="106" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="94"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="108"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" thickBot="1"/>
     <row r="4" spans="1:12" ht="15" customHeight="1" thickTop="1">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="111" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="98"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="99"/>
-      <c r="K4" s="95" t="s">
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="113"/>
+      <c r="K4" s="109" t="s">
         <v>52</v>
       </c>
-      <c r="L4" s="96"/>
+      <c r="L4" s="110"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1">
-      <c r="A5" s="100"/>
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="101"/>
-      <c r="I5" s="102"/>
+      <c r="A5" s="114"/>
+      <c r="B5" s="115"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
+      <c r="H5" s="115"/>
+      <c r="I5" s="116"/>
       <c r="K5" s="17" t="s">
         <v>53</v>
       </c>
@@ -3991,15 +3991,15 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1">
-      <c r="A6" s="100"/>
-      <c r="B6" s="101"/>
-      <c r="C6" s="101"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
-      <c r="H6" s="101"/>
-      <c r="I6" s="102"/>
+      <c r="A6" s="114"/>
+      <c r="B6" s="115"/>
+      <c r="C6" s="115"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="116"/>
       <c r="K6" s="19" t="s">
         <v>55</v>
       </c>
@@ -4008,15 +4008,15 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="103"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104"/>
-      <c r="I7" s="105"/>
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="119"/>
       <c r="K7" s="21" t="s">
         <v>57</v>
       </c>
@@ -4071,13 +4071,13 @@
         <f ca="1">MOD(Sheet2!B28,1000)+1000</f>
         <v>1066</v>
       </c>
-      <c r="F11" s="97" t="s">
+      <c r="F11" s="111" t="s">
         <v>49</v>
       </c>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="99"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="113"/>
       <c r="K11" s="26" t="s">
         <v>63</v>
       </c>
@@ -4093,11 +4093,11 @@
       </c>
       <c r="C12" s="35"/>
       <c r="D12" s="36"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="105"/>
+      <c r="F12" s="117"/>
+      <c r="G12" s="118"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="118"/>
+      <c r="J12" s="119"/>
       <c r="K12" s="27" t="s">
         <v>64</v>
       </c>
@@ -4124,13 +4124,13 @@
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="38"/>
-      <c r="F14" s="75" t="s">
+      <c r="F14" s="96" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="76"/>
-      <c r="H14" s="76"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="77"/>
+      <c r="G14" s="97"/>
+      <c r="H14" s="97"/>
+      <c r="I14" s="97"/>
+      <c r="J14" s="98"/>
       <c r="K14" s="28" t="s">
         <v>83</v>
       </c>
@@ -4146,11 +4146,11 @@
       </c>
       <c r="C15" s="37"/>
       <c r="D15" s="38"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="80"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="100"/>
+      <c r="H15" s="100"/>
+      <c r="I15" s="100"/>
+      <c r="J15" s="101"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" thickBot="1">
       <c r="A16">
@@ -4162,11 +4162,11 @@
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="38"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="82"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="83"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="103"/>
+      <c r="H16" s="103"/>
+      <c r="I16" s="103"/>
+      <c r="J16" s="104"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" thickBot="1">
       <c r="A17">
@@ -4189,13 +4189,13 @@
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="38"/>
-      <c r="F18" s="66" t="s">
+      <c r="F18" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="G18" s="67"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="68"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="65"/>
       <c r="K18" s="44"/>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1">
@@ -4208,13 +4208,13 @@
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="38"/>
-      <c r="F19" s="66" t="s">
+      <c r="F19" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="67"/>
-      <c r="H19" s="67"/>
-      <c r="I19" s="67"/>
-      <c r="J19" s="68"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="65"/>
       <c r="K19" s="42"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" thickBot="1">
@@ -4227,13 +4227,13 @@
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="38"/>
-      <c r="F20" s="66" t="s">
+      <c r="F20" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="G20" s="67"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="68"/>
+      <c r="G20" s="72"/>
+      <c r="H20" s="72"/>
+      <c r="I20" s="72"/>
+      <c r="J20" s="65"/>
       <c r="K20" s="42"/>
     </row>
     <row r="21" spans="1:11">
@@ -4353,49 +4353,49 @@
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.42578125" customWidth="1"/>
     <col min="13" max="13" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1"/>
     <row r="2" spans="1:12" ht="18.75" thickBot="1">
-      <c r="F2" s="92" t="s">
+      <c r="F2" s="106" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="94"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="108"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" thickBot="1"/>
     <row r="4" spans="1:12" ht="15" customHeight="1" thickTop="1">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="98"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="99"/>
-      <c r="K4" s="106" t="s">
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="113"/>
+      <c r="K4" s="120" t="s">
         <v>52</v>
       </c>
-      <c r="L4" s="107"/>
+      <c r="L4" s="121"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1">
-      <c r="A5" s="100"/>
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="101"/>
-      <c r="I5" s="102"/>
+      <c r="A5" s="114"/>
+      <c r="B5" s="115"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
+      <c r="H5" s="115"/>
+      <c r="I5" s="116"/>
       <c r="K5" s="17" t="s">
         <v>53</v>
       </c>
@@ -4404,15 +4404,15 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1">
-      <c r="A6" s="100"/>
-      <c r="B6" s="101"/>
-      <c r="C6" s="101"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
-      <c r="H6" s="101"/>
-      <c r="I6" s="102"/>
+      <c r="A6" s="114"/>
+      <c r="B6" s="115"/>
+      <c r="C6" s="115"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="116"/>
       <c r="K6" s="19" t="s">
         <v>55</v>
       </c>
@@ -4421,15 +4421,15 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="103"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104"/>
-      <c r="I7" s="105"/>
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="119"/>
       <c r="K7" s="21" t="s">
         <v>57</v>
       </c>
@@ -4484,13 +4484,13 @@
         <f ca="1">MOD(Sheet2!B28,1000)+1000</f>
         <v>1066</v>
       </c>
-      <c r="F11" s="97" t="s">
+      <c r="F11" s="111" t="s">
         <v>49</v>
       </c>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="99"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="113"/>
       <c r="K11" s="26" t="s">
         <v>63</v>
       </c>
@@ -4506,11 +4506,11 @@
       </c>
       <c r="C12" s="47"/>
       <c r="D12" s="48"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="105"/>
+      <c r="F12" s="117"/>
+      <c r="G12" s="118"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="118"/>
+      <c r="J12" s="119"/>
       <c r="K12" s="27" t="s">
         <v>64</v>
       </c>
@@ -4538,13 +4538,13 @@
       <c r="C14" s="49"/>
       <c r="D14" s="50"/>
       <c r="E14" s="16"/>
-      <c r="F14" s="75" t="s">
+      <c r="F14" s="96" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="76"/>
-      <c r="H14" s="76"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="77"/>
+      <c r="G14" s="97"/>
+      <c r="H14" s="97"/>
+      <c r="I14" s="97"/>
+      <c r="J14" s="98"/>
       <c r="K14" s="27" t="s">
         <v>83</v>
       </c>
@@ -4560,11 +4560,11 @@
       </c>
       <c r="C15" s="49"/>
       <c r="D15" s="50"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="80"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="100"/>
+      <c r="H15" s="100"/>
+      <c r="I15" s="100"/>
+      <c r="J15" s="101"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" thickBot="1">
       <c r="A16">
@@ -4576,11 +4576,11 @@
       </c>
       <c r="C16" s="49"/>
       <c r="D16" s="50"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="82"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="83"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="103"/>
+      <c r="H16" s="103"/>
+      <c r="I16" s="103"/>
+      <c r="J16" s="104"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" thickBot="1">
       <c r="A17">
@@ -4603,13 +4603,13 @@
       </c>
       <c r="C18" s="49"/>
       <c r="D18" s="50"/>
-      <c r="F18" s="66" t="s">
+      <c r="F18" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="G18" s="67"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="68"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="65"/>
       <c r="K18" s="44"/>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1">
@@ -4622,13 +4622,13 @@
       </c>
       <c r="C19" s="49"/>
       <c r="D19" s="50"/>
-      <c r="F19" s="66" t="s">
+      <c r="F19" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="G19" s="67"/>
-      <c r="H19" s="67"/>
-      <c r="I19" s="67"/>
-      <c r="J19" s="68"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="65"/>
       <c r="K19" s="42"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" thickBot="1">
@@ -4641,13 +4641,13 @@
       </c>
       <c r="C20" s="49"/>
       <c r="D20" s="50"/>
-      <c r="F20" s="66" t="s">
+      <c r="F20" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="G20" s="67"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="68"/>
+      <c r="G20" s="72"/>
+      <c r="H20" s="72"/>
+      <c r="I20" s="72"/>
+      <c r="J20" s="65"/>
       <c r="K20" s="42"/>
     </row>
     <row r="21" spans="1:11">
@@ -6292,54 +6292,54 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="6" spans="3:8">
-      <c r="C6" s="108" t="s">
+      <c r="C6" s="122" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
     </row>
     <row r="7" spans="3:8">
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="108"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="122"/>
+      <c r="G7" s="122"/>
+      <c r="H7" s="122"/>
     </row>
     <row r="8" spans="3:8">
-      <c r="C8" s="108"/>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="108"/>
+      <c r="C8" s="122"/>
+      <c r="D8" s="122"/>
+      <c r="E8" s="122"/>
+      <c r="F8" s="122"/>
+      <c r="G8" s="122"/>
+      <c r="H8" s="122"/>
     </row>
     <row r="9" spans="3:8">
-      <c r="C9" s="108"/>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="108"/>
+      <c r="C9" s="122"/>
+      <c r="D9" s="122"/>
+      <c r="E9" s="122"/>
+      <c r="F9" s="122"/>
+      <c r="G9" s="122"/>
+      <c r="H9" s="122"/>
     </row>
     <row r="10" spans="3:8">
-      <c r="C10" s="108"/>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="108"/>
+      <c r="C10" s="122"/>
+      <c r="D10" s="122"/>
+      <c r="E10" s="122"/>
+      <c r="F10" s="122"/>
+      <c r="G10" s="122"/>
+      <c r="H10" s="122"/>
     </row>
     <row r="11" spans="3:8">
-      <c r="C11" s="108"/>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="122"/>
+      <c r="F11" s="122"/>
+      <c r="G11" s="122"/>
+      <c r="H11" s="122"/>
     </row>
   </sheetData>
   <customSheetViews>
